--- a/development/service-ops-api/src/main/resources/templates/excel/dispatch-template.xlsx
+++ b/development/service-ops-api/src/main/resources/templates/excel/dispatch-template.xlsx
@@ -498,13 +498,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D500"/>
+  <dimension ref="A1:E500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -535,6 +536,11 @@
           <t>배송지주소 *</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>출발지 주소 (선택)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -557,6 +563,11 @@
           <t>서울특별시 강남구 테헤란로 123</t>
         </is>
       </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 테헤란로 1</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -3574,7 +3585,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="B3:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
